--- a/outputs/FNX-20260701-003_Lot_217_Hawke_Lane.xlsx
+++ b/outputs/FNX-20260701-003_Lot_217_Hawke_Lane.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consistency Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Takeoff" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consistency Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Takeoff" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="002C3E50"/>
         <bgColor rgb="002C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F8F5"/>
+        <bgColor rgb="00E8F8F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,8 +110,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDECEF"/>
-        <bgColor rgb="00FDECEF"/>
+        <fgColor rgb="00FDF7F2"/>
+        <bgColor rgb="00FDF7F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2FDF8"/>
+        <bgColor rgb="00F2FDF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,28 +162,22 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -179,6 +185,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -604,7 +628,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -615,7 +639,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>92.1%</t>
         </is>
       </c>
     </row>
@@ -658,372 +682,66 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>18-09AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
+          <t>12-12ASD-DG-LOW E</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Type Mismatch</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Glazing mismatch for 18-09AAW-DG-LOW E (Bedroom 2): Plans 'Double glazed low E' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
+          <t>Type mismatch for 12-12ASD-DG-LOW E (Bedroom 3): Plans 'sliding door' vs NatHERS 'awning'.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>18-09AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
+          <t>09-09AAW-OBS-DG</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Glazing Mismatch</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Frame mismatch for 18-09AAW-DG-LOW E (Bedroom 2): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
+          <t>Glazing mismatch for 09-09AAW-OBS-DG (Ensuite): Plans 'Obscure, Double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>15-18AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+          <t>09-09AAW-OBS-DG</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Glazing Mismatch</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Glazing mismatch for 15-18AAW-DG-LOW E (Master Bedroom): Plans 'Double glazed low E' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
+          <t>Glazing mismatch for 09-09AAW-OBS-DG (Bath): Plans 'Obscure, Double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>15-18AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
+          <t>Opening 22</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 15-18AAW-DG-LOW E (Master Bedroom): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>15-18AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for 15-18AAW-DG-LOW E (Kitchen/Dining/Family/Entry): Plans 'Double glazed low E' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>15-18AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 15-18AAW-DG-LOW E (Kitchen/Dining/Family/Entry): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>15-06AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for 15-06AAW-DG-LOW E (Kitchen/Dining/- Family/Entry): Plans 'Double glazed low E' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>15-06AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 15-06AAW-DG-LOW E (Kitchen/Dining/- Family/Entry): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>21-18ASD-DG</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 21-18ASD-DG (Kitchen/Dining/- Family/Entry): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>15-18AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for 15-18AAW-DG-LOW E (Kitchen/Dining/- Family/Entry): Plans 'Double glazed low E' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>15-18AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 15-18AAW-DG-LOW E (Kitchen/Dining/- Family/Entry): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>12-12ASD-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Type Mismatch</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Type mismatch for 12-12ASD-DG-LOW E (Bedroom 3): Plans 'sliding door' vs NatHERS 'awning'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>12-12ASD-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for 12-12ASD-DG-LOW E (Bedroom 3): Plans 'Double glazed low E' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>12-12ASD-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 12-12ASD-DG-LOW E (Bedroom 3): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>12-12ASD-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Low Confidence</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>12-12ASD-DG-LOW E (Bedroom 3): Low confidence (65%) � verify specs manually.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>09-09AAW-OBS-DG</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for 09-09AAW-OBS-DG (Ensuite): Plans 'Obscure double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>09-09AAW-OBS-DG</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 09-09AAW-OBS-DG (Ensuite): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>09-09AAW-OBS-DG</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for 09-09AAW-OBS-DG (Bath): Plans 'Obscure double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>09-09AAW-OBS-DG</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 09-09AAW-OBS-DG (Bath): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>18-09AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for 18-09AAW-DG-LOW E (Bedroom 2): Plans 'Double glazed low E' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>18-09AAW-DG-LOW E</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Frame Mismatch</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Frame mismatch for 18-09AAW-DG-LOW E (Bedroom 2): Plans 'Aluminium' vs NatHERS 'Timber'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Opening 22</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Opening 22 (Kitchen/Dining/- Family/Entry) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
@@ -1049,652 +767,652 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="68" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Lot 217 Hawke Lane — Takeoff Takeoff schedule</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>W/D Number</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Height (mm)</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Width (mm)</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>Orientation</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>Glazing Type</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>U-value</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>SHGC</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Frame Material</t>
         </is>
       </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>Source Reference</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Bedroom 2</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>18-09AAW-DG-LOW E</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr"/>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I3" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K3" s="15" t="n">
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Master Bedroom</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>15-18AAW-DG-LOW E</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="16" t="n">
         <v>1500</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr"/>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K4" s="15" t="n">
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Kitchen/Dining/Family/Entry</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>15-18AAW-DG-LOW E</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="16" t="n">
         <v>1500</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K5" s="15" t="n">
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Kitchen/Dining/- Family/Entry</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>15-06AAW-DG-LOW E</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>600</v>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr"/>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="n">
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Kitchen/Dining/- Family/Entry</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>21-18ASD-DG</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="19" t="n">
         <v>2100</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>541/542 Al Sliding Door DG 6-1</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>541/542 Al Sliding Door DG 6-10-6ClimaTech</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K7" s="15" t="n">
+      <c r="K7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Kitchen/Dining/- Family/Entry</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>15-18AAW-DG-LOW E</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="n">
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Bedroom 3</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>12-12ASD-DG-LOW E</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="n">
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Ensuite</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>09-09AAW-OBS-DG</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="n">
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>09-09AAW-OBS-DG</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="n">
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Bedroom 2</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>18-09AAW-DG-LOW E</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>900</v>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr"/>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>Thermaview Awning Window (413</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>Timber</t>
-        </is>
-      </c>
-      <c r="K12" s="15" t="n">
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Kitchen/Dining/- Family/Entry</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Opening 22</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="22" t="n">
         <v>2040</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="22" t="n">
         <v>820</v>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>casement</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="H13" s="21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>

--- a/outputs/FNX-20260701-003_Lot_217_Hawke_Lane.xlsx
+++ b/outputs/FNX-20260701-003_Lot_217_Hawke_Lane.xlsx
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -110,12 +110,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDF7F2"/>
-        <bgColor rgb="00FDF7F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2FDF8"/>
         <bgColor rgb="00F2FDF8"/>
       </patternFill>
@@ -147,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -194,15 +188,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -570,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -628,7 +613,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +624,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>87.4%</t>
         </is>
       </c>
     </row>
@@ -709,7 +694,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Glazing mismatch for 09-09AAW-OBS-DG (Ensuite): Plans 'Obscure, Double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
+          <t>Glazing mismatch for 09-09AAW-OBS-DG (Ensuite): Plans 'Obscure double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
         </is>
       </c>
     </row>
@@ -726,22 +711,39 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Glazing mismatch for 09-09AAW-OBS-DG (Bath): Plans 'Obscure, Double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
+          <t>Glazing mismatch for 09-09AAW-OBS-DG (Bath): Plans 'Obscure double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>Opening 13</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Opening 13 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>Opening 22</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Opening 22 (Kitchen/Dining/- Family/Entry) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
@@ -1157,52 +1159,52 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Bedroom 3</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>12-12ASD-DG-LOW E</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="16" t="n">
         <v>1200</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="16" t="n">
         <v>1200</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>awning</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr</t>
         </is>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="15" t="n">
         <v>3.78</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="15" t="n">
         <v>0.48</v>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="K9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t>Plans p.4 / NatHERS p.14, p.15</t>
         </is>
@@ -1320,7 +1322,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>18-09AAW-DG-LOW E</t>
+          <t>Opening 13</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
@@ -1360,57 +1362,57 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.14, p.15</t>
+          <t>NatHERS p.14, p.15</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Kitchen/Dining/- Family/Entry</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Opening 22</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="16" t="n">
         <v>2040</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="16" t="n">
         <v>820</v>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>casement</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Aluminium A SG Clear</t>
         </is>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="H13" s="15" t="n">
         <v>6.7</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="15" t="n">
         <v>0.57</v>
       </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K13" s="22" t="n">
+      <c r="K13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>NatHERS p.14, p.15</t>
         </is>

--- a/outputs/FNX-20260701-003_Lot_217_Hawke_Lane.xlsx
+++ b/outputs/FNX-20260701-003_Lot_217_Hawke_Lane.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
     </row>
@@ -687,14 +687,14 @@
           <t>09-09AAW-OBS-DG</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Obscure Glazing Note</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Glazing mismatch for 09-09AAW-OBS-DG (Ensuite): Plans 'Obscure double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
+          <t>Obscure glazing noted on plans for 09-09AAW-OBS-DG (Ensuite) — clear/obscure share U-value/SHGC; plan adds detail.</t>
         </is>
       </c>
     </row>
@@ -704,14 +704,14 @@
           <t>09-09AAW-OBS-DG</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Obscure Glazing Note</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Glazing mismatch for 09-09AAW-OBS-DG (Bath): Plans 'Obscure double glazed' vs NatHERS 'Thermaview Awning Window (413 System) DG 6.38LamClr/10/6.38CPClr'.</t>
+          <t>Obscure glazing noted on plans for 09-09AAW-OBS-DG (Bath) — clear/obscure share U-value/SHGC; plan adds detail.</t>
         </is>
       </c>
     </row>
